--- a/news_daily/2026-10-13.xlsx
+++ b/news_daily/2026-10-13.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1011,6 +1027,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1061,13 +1081,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1120,7 +1144,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>4870844048e446aaa25497c4d6af2f38</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>0aabc58ddebe64314dacdbbd</t>
@@ -1141,7 +1169,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1185,6 +1217,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1359,6 +1403,10 @@
       </c>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1533,6 +1581,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1699,6 +1751,10 @@
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1873,6 +1929,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2047,183 +2107,207 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Walt Disney Company (The)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-10-13T15:05:26+08:00</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Character.AI files for bankruptcy reorganization and agrees to sell some assets to Disney</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>'-0.027</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2708239</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Character.AI 申請破產重組並同意將部分資產出售給迪士尼</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>bankruptcy</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>4dc253c766404bb5b5428602d86624f9</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>537fe1c0c6c0f9467a947e80</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>d4871428d73a5f522ce6f6e8</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>'-0.027</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2708239</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr">
-        <is>
-          <t>Character.AI 申請破產重組並同意將部分資產出售給迪士尼</t>
-        </is>
-      </c>
-      <c r="X9" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA9" s="5" t="inlineStr"/>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr">
-        <is>
-          <t>537fe1c0c6c0f9467a947e80</t>
-        </is>
-      </c>
-      <c r="AD9" s="5" t="inlineStr">
-        <is>
-          <t>d4871428d73a5f522ce6f6e8</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr"/>
-      <c r="AF9" s="5" t="inlineStr"/>
-      <c r="AG9" s="5" t="inlineStr"/>
-      <c r="AH9" s="5" t="inlineStr"/>
-      <c r="AI9" s="5" t="inlineStr"/>
-      <c r="AJ9" s="5" t="inlineStr"/>
-      <c r="AK9" s="5" t="inlineStr"/>
-      <c r="AL9" s="5" t="inlineStr"/>
-      <c r="AM9" s="5" t="inlineStr"/>
-      <c r="AN9" s="5" t="inlineStr"/>
-      <c r="AO9" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="5" t="inlineStr"/>
-      <c r="AQ9" s="5" t="inlineStr"/>
-      <c r="AR9" s="5" t="inlineStr"/>
-      <c r="AS9" s="5" t="inlineStr"/>
-      <c r="AT9" s="5" t="inlineStr"/>
-      <c r="AU9" s="5" t="inlineStr"/>
-      <c r="AV9" s="5" t="inlineStr"/>
-      <c r="AW9" s="5" t="inlineStr"/>
-      <c r="AX9" s="5" t="inlineStr"/>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
-      <c r="BB9" s="5" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="BC9" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE9" s="5" t="inlineStr">
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="5" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="5" t="inlineStr"/>
-      <c r="BH9" s="5" t="inlineStr"/>
+      <c r="BG9" s="2" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH9"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2234,7 +2318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2381,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2600,6 +2688,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2650,13 +2758,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -2709,7 +2821,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>4870844048e446aaa25497c4d6af2f38</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>0aabc58ddebe64314dacdbbd</t>
@@ -2730,7 +2846,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -2774,6 +2894,18 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2940,183 +3072,13 @@
         </is>
       </c>
       <c r="BH3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13T15:05:26+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Character.AI files for bankruptcy reorganization and agrees to sell some assets to Disney</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>'-0.027</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2708239</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="inlineStr">
-        <is>
-          <t>Character.AI 申請破產重組並同意將部分資產出售給迪士尼</t>
-        </is>
-      </c>
-      <c r="X4" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z4" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA4" s="5" t="inlineStr"/>
-      <c r="AB4" s="5" t="inlineStr"/>
-      <c r="AC4" s="5" t="inlineStr">
-        <is>
-          <t>537fe1c0c6c0f9467a947e80</t>
-        </is>
-      </c>
-      <c r="AD4" s="5" t="inlineStr">
-        <is>
-          <t>d4871428d73a5f522ce6f6e8</t>
-        </is>
-      </c>
-      <c r="AE4" s="5" t="inlineStr"/>
-      <c r="AF4" s="5" t="inlineStr"/>
-      <c r="AG4" s="5" t="inlineStr"/>
-      <c r="AH4" s="5" t="inlineStr"/>
-      <c r="AI4" s="5" t="inlineStr"/>
-      <c r="AJ4" s="5" t="inlineStr"/>
-      <c r="AK4" s="5" t="inlineStr"/>
-      <c r="AL4" s="5" t="inlineStr"/>
-      <c r="AM4" s="5" t="inlineStr"/>
-      <c r="AN4" s="5" t="inlineStr"/>
-      <c r="AO4" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="5" t="inlineStr"/>
-      <c r="AQ4" s="5" t="inlineStr"/>
-      <c r="AR4" s="5" t="inlineStr"/>
-      <c r="AS4" s="5" t="inlineStr"/>
-      <c r="AT4" s="5" t="inlineStr"/>
-      <c r="AU4" s="5" t="inlineStr"/>
-      <c r="AV4" s="5" t="inlineStr"/>
-      <c r="AW4" s="5" t="inlineStr"/>
-      <c r="AX4" s="5" t="inlineStr"/>
-      <c r="AY4" s="5" t="inlineStr"/>
-      <c r="AZ4" s="5" t="inlineStr"/>
-      <c r="BA4" s="5" t="inlineStr"/>
-      <c r="BB4" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC4" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE4" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="5" t="inlineStr"/>
-      <c r="BH4" s="5" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr"/>
+      <c r="BL3" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH4"/>
+  <autoFilter ref="A1:BL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3127,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3190,6 +3152,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3491,6 +3457,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3667,183 +3653,13 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-13T15:05:26+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Character.AI files for bankruptcy reorganization and agrees to sell some assets to Disney</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>'-0.027</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2708239</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
-        <is>
-          <t>Character.AI 申請破產重組並同意將部分資產出售給迪士尼</t>
-        </is>
-      </c>
-      <c r="X3" s="5" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="5" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z3" s="5" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA3" s="5" t="inlineStr"/>
-      <c r="AB3" s="5" t="inlineStr"/>
-      <c r="AC3" s="5" t="inlineStr">
-        <is>
-          <t>537fe1c0c6c0f9467a947e80</t>
-        </is>
-      </c>
-      <c r="AD3" s="5" t="inlineStr">
-        <is>
-          <t>d4871428d73a5f522ce6f6e8</t>
-        </is>
-      </c>
-      <c r="AE3" s="5" t="inlineStr"/>
-      <c r="AF3" s="5" t="inlineStr"/>
-      <c r="AG3" s="5" t="inlineStr"/>
-      <c r="AH3" s="5" t="inlineStr"/>
-      <c r="AI3" s="5" t="inlineStr"/>
-      <c r="AJ3" s="5" t="inlineStr"/>
-      <c r="AK3" s="5" t="inlineStr"/>
-      <c r="AL3" s="5" t="inlineStr"/>
-      <c r="AM3" s="5" t="inlineStr"/>
-      <c r="AN3" s="5" t="inlineStr"/>
-      <c r="AO3" s="5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="5" t="inlineStr"/>
-      <c r="AQ3" s="5" t="inlineStr"/>
-      <c r="AR3" s="5" t="inlineStr"/>
-      <c r="AS3" s="5" t="inlineStr"/>
-      <c r="AT3" s="5" t="inlineStr"/>
-      <c r="AU3" s="5" t="inlineStr"/>
-      <c r="AV3" s="5" t="inlineStr"/>
-      <c r="AW3" s="5" t="inlineStr"/>
-      <c r="AX3" s="5" t="inlineStr"/>
-      <c r="AY3" s="5" t="inlineStr"/>
-      <c r="AZ3" s="5" t="inlineStr"/>
-      <c r="BA3" s="5" t="inlineStr"/>
-      <c r="BB3" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC3" s="5" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="5" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="5" t="inlineStr"/>
-      <c r="BH3" s="5" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3854,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3917,6 +3733,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4220,9 +4040,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4233,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4283,134 +4123,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4420,46 +4260,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4468,12 +4342,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4483,90 +4357,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4576,94 +4454,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4671,89 +4549,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-13.xlsx
+++ b/news_daily/2026-10-13.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1260,32 +1260,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1338,7 +1338,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>00a68221d4874b85a75c3e4578009043</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>da685cad4e83ef19e7ccbee9</t>
@@ -1361,7 +1365,7 @@
       <c r="AN4" s="2" t="inlineStr"/>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP4" s="2" t="inlineStr"/>
@@ -1403,10 +1407,22 @@
       </c>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1635,13 +1651,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1694,7 +1714,11 @@
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>63b0074039e8413a90dc79282e6dc112</t>
+        </is>
+      </c>
       <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>78091de5dc53c869e71d7148</t>
@@ -1715,7 +1739,11 @@
       <c r="AL6" s="4" t="inlineStr"/>
       <c r="AM6" s="4" t="inlineStr"/>
       <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="4" t="inlineStr"/>
       <c r="AQ6" s="4" t="inlineStr"/>
       <c r="AR6" s="4" t="inlineStr"/>
@@ -1753,8 +1781,16 @@
       <c r="BH6" s="4" t="inlineStr"/>
       <c r="BI6" s="4" t="inlineStr"/>
       <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2956,13 +2992,17 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -3015,7 +3055,11 @@
         </is>
       </c>
       <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>63b0074039e8413a90dc79282e6dc112</t>
+        </is>
+      </c>
       <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>78091de5dc53c869e71d7148</t>
@@ -3036,7 +3080,11 @@
       <c r="AL3" s="4" t="inlineStr"/>
       <c r="AM3" s="4" t="inlineStr"/>
       <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="4" t="inlineStr"/>
       <c r="AQ3" s="4" t="inlineStr"/>
       <c r="AR3" s="4" t="inlineStr"/>
@@ -3074,8 +3122,16 @@
       <c r="BH3" s="4" t="inlineStr"/>
       <c r="BI3" s="4" t="inlineStr"/>
       <c r="BJ3" s="4" t="inlineStr"/>
-      <c r="BK3" s="4" t="inlineStr"/>
-      <c r="BL3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL3"/>
@@ -3089,7 +3145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3480,186 +3536,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Intuitive Surgical</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13T18:58:26+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Johnson &amp; Johnson medical device sales weaken, shares fall</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>股價下跌</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.963</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-ISRG/news/</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>強生醫療器材銷售疲軟，股價下跌</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>PRICE_MOVEMENT</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>shares fall</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>da685cad4e83ef19e7ccbee9</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>b16bab7f2ddb062afc3851ca</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>ISRG</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-10-13.xlsx
+++ b/news_daily/2026-10-13.xlsx
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>56f336da19c4494e9bd97dfd876918c7</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>64aa111589be5cba7c92ed35</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1029,8 +1041,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1458,28 +1478,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1523,7 +1547,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1532,7 +1556,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>11040398cac24740a4be39f1a5e85119</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>b563eff02015245b4bcd2eda</t>
@@ -1553,7 +1581,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1597,10 +1629,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1841,13 +1885,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1900,7 +1948,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>bec8a1edc4fe49e8ac3b94a824063c07</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>9a0e140ca7f6f9fd564dcf15</t>
@@ -1921,7 +1973,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1967,8 +2023,16 @@
       <c r="BH7" s="2" t="inlineStr"/>
       <c r="BI7" s="2" t="inlineStr"/>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2019,13 +2083,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2078,7 +2146,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>4479f7cc1ff54314b29eae2715f60716</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>e116b66879de36a1e184f2e7</t>
@@ -2099,7 +2171,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2145,8 +2221,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">

--- a/news_daily/2026-10-13.xlsx
+++ b/news_daily/2026-10-13.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,21 +71,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -463,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL9"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2426,8 +2415,158 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13T09:33:30+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Bernstein downgrades AT&amp;T to 'market perform'</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>分析師降評</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>規則</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.666</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/news/5323387</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>伯恩斯坦將 AT&amp;T 評級下調至“與市場表現持平”</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>ANALYST_DOWNGRADE</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>downgrade</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>5561e078da65c13f043b1ebb</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>e42b59b00a7a79cc7f349e65</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr"/>
+      <c r="BC10" s="2" t="inlineStr"/>
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr"/>
+      <c r="BF10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BL9"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
